--- a/Documents/caapd-facturacion/escritorio/Base de datos/PADRON_MES_2026-08.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos/PADRON_MES_2026-08.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;S/. &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,7 +39,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -66,7 +66,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00334155"/>
       <sz val="10"/>
     </font>
     <font>
@@ -76,12 +81,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="00475569"/>
+      <name val="Courier New"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -96,14 +100,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CBD5E1"/>
-        <bgColor rgb="00CBD5E1"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
         <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0015803D"/>
+        <bgColor rgb="0015803D"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,24 +151,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,27 +535,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CAAPD ISPACAS — PADRÓN Y RESPALDO DEL MES 2026-08</t>
+          <t>CAAPD ISPACAS — ARCHIVO DE RESPALDO INTEGRAL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Archivo de prueba generado deterministamente para verificación integral.</t>
-        </is>
-      </c>
-    </row>
+          <t>Este archivo contiene la copia completa de la base de datos para contingencia y restauración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -577,7 +589,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:54:39</t>
+          <t>2026-10-15 06:26:17</t>
         </is>
       </c>
     </row>
@@ -618,11 +630,11 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Total Filas Planilla</t>
+          <t>Total Documentos Mes</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -647,15 +659,46 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>TIPO: ARCHIVO DE PRUEBA</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>SI</t>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES DE RESTAURACIÓN:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>1. Para restaurar automáticamente ejecute:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   python scripts/restaurar_excel.py --archivo respaldos/RESPALDO_2026-08.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2. El script valida los conteos y la suma de control de esta hoja antes y después de restaurar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>3. Las hojas por sector contienen a la derecha un bloque gris con los datos técnicos para reconstrucción exacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>4. No altere los valores de ID Usuario ni las columnas del bloque gris para garantizar consistencia.</t>
         </is>
       </c>
     </row>
@@ -673,290 +716,291 @@
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — AYACUCHO (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: AYACUCHO — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000527</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>2001887</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>CHAUCAYANQUI ALVAREZ, CARLOS ALEJO</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000113</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>30771152</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
+      <c r="S4" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.ayacucho@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>16,7,6,17,10</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>16.0,7.0,6.0,17.0,10.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>9</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -968,108 +1012,108 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000528</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>6593681</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>CHAUCAYANQUI ALVAREZ, CLEMENTE</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="11" t="n">
         <v>940</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>954</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000114</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr"/>
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>30770229</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.ayacucho@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>8,17,7,16,17</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>8.0,17.0,7.0,16.0,17.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>14</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -1081,108 +1125,108 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000529</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>220014925</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>SURCO VILLENA, SUSY BETTY</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>240</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>249</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>000000115</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr"/>
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>30770890</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.ayacucho@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>15,12,6,6,7</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="n">
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>15.0,12.0,6.0,6.0,7.0</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="n">
         <v>9</v>
       </c>
       <c r="Y6" s="14" t="n">
@@ -1194,108 +1238,108 @@
       <c r="AA6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13" t="n">
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>000530</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>6563926</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>TORRES COA, CILA CAMILA</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>221</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>238</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>000000116</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr"/>
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>30770036</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>lector.ayacucho@prueba.local</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>14,15,6,14,9</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>14.0,15.0,6.0,14.0,9.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>17</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -1307,112 +1351,112 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>000531</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>6563939</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>TORRES HUAMANI, AMELIA BENITA</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>463</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="11" t="n">
         <v>478</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>000000117</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
         <v>27.5</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>30778043</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" s="13" t="n">
+      <c r="S8" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>lector.ayacucho@prueba.local</t>
         </is>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>17,14,12,9,13</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="n">
+      <c r="W8" s="14" t="inlineStr">
+        <is>
+          <t>17.0,14.0,12.0,9.0,13.0</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="n">
         <v>15</v>
       </c>
       <c r="Y8" s="14" t="n">
@@ -1424,10 +1468,10 @@
       <c r="AA8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="13" t="n">
+      <c r="AB8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1445,290 +1489,291 @@
   <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — CHAUPICERCA (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: CHAUPICERCA — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000704</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>220017513</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>CASTRO USCAMAYTA ELIANA</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>CHAUPICERCA S/N</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000132</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>80313677</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="S4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.chaupicerca@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>18,6,18,18,0</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>18.0,6.0,18.0,18.0,0.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -1740,112 +1785,112 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000534</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>6593461</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>NEYRA DE USCAMAYTA, MANUELA ANA</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>CHAUPICERCA S/N</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000133</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>30769321</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.chaupicerca@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>12,11,10,8,9</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>12.0,11.0,10.0,8.0,9.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>2</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -1857,112 +1902,112 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000533</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>6593433</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ROMERO CHAUCAYANQUI JUSTO MARCELO</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>CHAUPICERCA S/N</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>535</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>546</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>000000134</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>21.5</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>30769931-1</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.chaupicerca@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>11,7,7,12,7</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="n">
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>11.0,7.0,7.0,12.0,7.0</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="n">
         <v>11</v>
       </c>
       <c r="Y6" s="14" t="n">
@@ -1974,112 +2019,112 @@
       <c r="AA6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13" t="n">
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>000536</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>6593726</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>USCAMAYTA NEYRA, DAVID JESUS</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>CHAUPICERCA S/N</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>306</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>319</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>000000135</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>30769896</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>lector.chaupicerca@prueba.local</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>15,10,18,6,17</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>15.0,10.0,18.0,6.0,17.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>13</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -2091,10 +2136,10 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2112,290 +2157,291 @@
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="29" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — BARRIO DE CHAUPI (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: BARRIO DE CHAUPI — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000498</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>60062505</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ALFARO NEYRA DE CHUQUIYANQUI LUCIA POMPEYA</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>AV. CENTENARIO 102</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="11" t="n">
         <v>218</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>234</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000118</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>30769528</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
+      <c r="S4" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.chaupi@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>7,12,7,14,10</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>7.0,12.0,7.0,14.0,10.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>16</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -2407,112 +2453,112 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000308</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>60062454</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>ALFARO TORREZ, TATIANA PAOLA</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>JR. LIMA 45</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>121</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000119</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>45209656</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.chaupi@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>20,33,19,24,16</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>20.0,33.0,19.0,24.0,16.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>13</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -2524,195 +2570,191 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000308</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>18052517</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ALFARO TORREZ, TATIANA PAOLA</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>JR. LIMA 45</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>726</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>733</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr"/>
+      <c r="O6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr"/>
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>45209656</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.chaupi@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr"/>
+      <c r="W6" s="14" t="inlineStr"/>
+      <c r="X6" s="14" t="inlineStr"/>
+      <c r="Y6" s="14" t="inlineStr"/>
+      <c r="Z6" s="14" t="inlineStr"/>
+      <c r="AA6" s="14" t="inlineStr"/>
+      <c r="AB6" s="14" t="inlineStr"/>
+      <c r="AC6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>000274</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>009174</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>ALVAREZ VERA LELIS SOLNA</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>CALLE CHAUPI 12</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>481</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>492</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>000000120</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>30769348</t>
+        </is>
+      </c>
+      <c r="R7" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="S7" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>LEIDO</t>
+        </is>
+      </c>
+      <c r="U7" s="14" t="inlineStr">
+        <is>
+          <t>lector.chaupi@prueba.local</t>
+        </is>
+      </c>
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="13" t="n"/>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="13" t="n"/>
-      <c r="AC6" s="13" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>000274</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>009174</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>ALVAREZ VERA LELIS SOLNA</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CALLE CHAUPI 12</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>481</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>492</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>000000120</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Q7" s="12" t="inlineStr">
-        <is>
-          <t>30769348</t>
-        </is>
-      </c>
-      <c r="R7" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="S7" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" s="13" t="inlineStr">
-        <is>
-          <t>LEIDO</t>
-        </is>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
-        <is>
-          <t>lector.chaupi@prueba.local</t>
-        </is>
-      </c>
-      <c r="V7" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>10,13,16,11,8</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>10.0,13.0,16.0,11.0,8.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>11</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -2724,112 +2766,112 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>000746</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>23022187</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>ANGULO ESCOBAR, JEISVER ANTONIO</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>AV. CIRCUNVALACION 88</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>361</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="11" t="n">
         <v>377</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>000000121</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>46981924</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" s="13" t="n">
+      <c r="S8" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>lector.chaupi@prueba.local</t>
         </is>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>9,16,10,17,16</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="n">
+      <c r="W8" s="14" t="inlineStr">
+        <is>
+          <t>9.0,16.0,10.0,17.0,16.0</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="n">
         <v>16</v>
       </c>
       <c r="Y8" s="14" t="n">
@@ -2841,10 +2883,10 @@
       <c r="AA8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="13" t="n">
+      <c r="AB8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2862,290 +2904,291 @@
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — BARRIO DE LUCMANI (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: BARRIO DE LUCMANI — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000002</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>6659764</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ANTACHOQUE MOTA, JUANA HILDA</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>SECTOR LUCMANI 14</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="11" t="n">
         <v>350</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>359</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000122</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>30771072</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
+      <c r="S4" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.lucmani@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>15,16,8,14,17</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>15.0,16.0,8.0,14.0,17.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>9</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -3157,112 +3200,112 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000004</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>6585597</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>ANTACHOQUE VERA, JUAN JUSTO</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>SECTOR LUCMANI 22</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="11" t="n">
         <v>586</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>600</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000123</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>30769540</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.lucmani@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>13,12,10,16,17</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>13.0,12.0,10.0,16.0,17.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>14</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -3274,112 +3317,112 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000006</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>6582810</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>AYMARA HUAMANI, ALEJA</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>SECTOR LUCMANI 30</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>544</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>553</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>000000124</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>30770030</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.lucmani@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>16,11,18,18,6</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="n">
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>16.0,11.0,18.0,18.0,6.0</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="n">
         <v>9</v>
       </c>
       <c r="Y6" s="14" t="n">
@@ -3391,112 +3434,112 @@
       <c r="AA6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13" t="n">
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>000007</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>23015480</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>CABRERA CHAVEZ, ASISCLO</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>SECTOR LUCMANI 45</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>865</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>874</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>000000125</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>30770213</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>lector.lucmani@prueba.local</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>18,11,12,10,7</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>18.0,11.0,12.0,10.0,7.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>9</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -3508,112 +3551,112 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>000771</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>SIN_MEDIDOR</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>CONEXION SIN MEDIDOR 000771</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>LUCMANI S/N</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>000000126</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>SD-026</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="S8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>lector.lucmani@prueba.local</t>
         </is>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="n">
+      <c r="W8" s="14" t="inlineStr">
+        <is>
+          <t>0.0,0.0,0.0,0.0,0.0</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="14" t="n">
@@ -3625,10 +3668,10 @@
       <c r="AA8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="13" t="n">
+      <c r="AB8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3646,290 +3689,291 @@
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — BARRIO DE PACHAYZA (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: BARRIO DE PACHAYZA — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000089</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>6579582</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ALFARO LUQUE, MARIA</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>AV. PACHAYZA 5</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="11" t="n">
         <v>460</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>467</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000127</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>30770148</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
+      <c r="S4" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.pachayza@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>11,9,8,14,13</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>11.0,9.0,8.0,14.0,13.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>7</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -3941,112 +3985,112 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000092</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>21003057</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>ANTACHOQUE ANCO, YULY INES</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>AV. PACHAYZA 10</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="11" t="n">
         <v>1713</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>1725</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000128</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>SD-001</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.pachayza@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>17,11,9,16,13</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>17.0,11.0,9.0,16.0,13.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>12</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -4058,112 +4102,112 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000095</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>6659519</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>APAZA QUISPE, JOSE</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>JR. GRAU 44</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>841</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>859</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>000000129</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>02434916</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.pachayza@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>6,7,8,16,8</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="n">
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>6.0,7.0,8.0,16.0,8.0</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="n">
         <v>18</v>
       </c>
       <c r="Y6" s="14" t="n">
@@ -4175,112 +4219,112 @@
       <c r="AA6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13" t="n">
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>000098</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>6587963</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>CARPIO HUAMANI, JUAN VITALIANO</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>JR. BOLOGNESI 15</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>1032</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>1049</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>000000130</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>30769551-1</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>lector.pachayza@prueba.local</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>13,8,10,8,9</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>13.0,8.0,10.0,8.0,9.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>17</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -4292,112 +4336,112 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>000099</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>6579722</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>CARPIO LAZARO, NANCY CELSA</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>JR. BOLOGNESI 17</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>1472</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="11" t="n">
         <v>1487</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>000000131</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
         <v>27.5</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>30769551-2</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" s="13" t="n">
+      <c r="S8" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>lector.pachayza@prueba.local</t>
         </is>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>14,10,17,15,12</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="n">
+      <c r="W8" s="14" t="inlineStr">
+        <is>
+          <t>14.0,10.0,17.0,15.0,12.0</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="n">
         <v>15</v>
       </c>
       <c r="Y8" s="14" t="n">
@@ -4409,10 +4453,10 @@
       <c r="AA8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="13" t="n">
+      <c r="AB8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4430,290 +4474,291 @@
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN DE USUARIOS Y LECTURAS — HUAQUILLO (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PLANILLA SECTOR: HUAQUILLO — PERIODO 2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Fecha Lect.</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Conexión</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>N° Medidor</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Titular / Beneficiario</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Lect. Anterior</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lect. Actual</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Consumo (m³)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>N° Recibo</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Deuda Ant. (S/.)</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Deuda Actual (S/.)</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Fecha Pago</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>ID Usuario</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>Fecha Anterior</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>Consumo Anterior</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Estado Lectura</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>Registrado Por</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Historial m³</t>
         </is>
       </c>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>Consumo Total m³</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="Y3" s="10" t="inlineStr">
         <is>
           <t>Monto Agua</t>
         </is>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="10" t="inlineStr">
         <is>
           <t>Monto Desagüe</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AA3" s="10" t="inlineStr">
         <is>
           <t>Cargo Fijo</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="AB3" s="10" t="inlineStr">
         <is>
           <t>IGV</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AC3" s="10" t="inlineStr">
         <is>
           <t>Redondeo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>000055</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>6587782</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ALFARO NAVINTA, ANIBAL</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>HUAQUILLO CENTRO</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="11" t="n">
         <v>458</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="11" t="n">
         <v>473</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr"/>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>000000136</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11" t="n">
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>27.5</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>29302445</t>
         </is>
       </c>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" s="13" t="n">
+      <c r="S4" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>lector.huaquillo@prueba.local</t>
         </is>
       </c>
-      <c r="V4" s="13" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>12,15,7,12,12</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="n">
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>12.0,15.0,7.0,12.0,12.0</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="n">
         <v>15</v>
       </c>
       <c r="Y4" s="14" t="n">
@@ -4725,112 +4770,112 @@
       <c r="AA4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="13" t="n">
+      <c r="AB4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>000066</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>6659665</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>CALLA HUARSAYA, LUIS</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>HUAQUILLO ALTO</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="11" t="n">
         <v>496</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="11" t="n">
         <v>513</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>000000137</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>02150722</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="T5" s="13" t="inlineStr">
+      <c r="T5" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>lector.huaquillo@prueba.local</t>
         </is>
       </c>
-      <c r="V5" s="13" t="inlineStr">
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W5" s="13" t="inlineStr">
-        <is>
-          <t>14,10,14,6,16</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="n">
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>14.0,10.0,14.0,6.0,16.0</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="n">
         <v>17</v>
       </c>
       <c r="Y5" s="14" t="n">
@@ -4842,112 +4887,112 @@
       <c r="AA5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="13" t="n">
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>000059</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>6593586</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>CHALCO CORIMANYA, BLANCA DELIA</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>HUAQUILLO S/N</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>1544</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="11" t="n">
         <v>1560</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>000000138</t>
         </is>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>30769698</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>lector.huaquillo@prueba.local</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>16,14,18,10,18</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="n">
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>16.0,14.0,18.0,10.0,18.0</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="n">
         <v>16</v>
       </c>
       <c r="Y6" s="14" t="n">
@@ -4959,112 +5004,112 @@
       <c r="AA6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13" t="n">
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>000061</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>21003055</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>CHALCO HUAMANI, SAIDA</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>HUAQUILLO PRINCIPAL</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="11" t="n">
         <v>124</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>000000139</t>
         </is>
       </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="L7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>30769343</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="T7" s="13" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>lector.huaquillo@prueba.local</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>7,10,12,8,13</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="n">
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>7.0,10.0,12.0,8.0,13.0</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="n">
         <v>6</v>
       </c>
       <c r="Y7" s="14" t="n">
@@ -5076,112 +5121,112 @@
       <c r="AA7" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="13" t="n">
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>000070</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>6659861</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>HUAMANI CASTRO, BERTHA</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>HUAQUILLO BAJO</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="11" t="n">
         <v>664</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr"/>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>000000140</t>
         </is>
       </c>
-      <c r="L8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="L8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" s="13" t="n">
+      <c r="S8" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="T8" s="13" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>LEIDO</t>
         </is>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>lector.huaquillo@prueba.local</t>
         </is>
       </c>
-      <c r="V8" s="13" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>17,10,14,18,8</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="n">
+      <c r="W8" s="14" t="inlineStr">
+        <is>
+          <t>17.0,10.0,14.0,18.0,8.0</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="n">
         <v>14</v>
       </c>
       <c r="Y8" s="14" t="n">
@@ -5193,10 +5238,10 @@
       <c r="AA8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="13" t="n">
+      <c r="AB8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5214,1238 +5259,1239 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PADRÓN MAESTRO DE USUARIOS — CAAPD ISPACAS (2026-08)</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — PADRÓN MAESTRO DE USUARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>ID Usuario</t>
+          <t>id_usuario</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>N° Conexión</t>
+          <t>nro_conexion</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Nombre Completo</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>Dirección</t>
+          <t>direccion</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>codigo_categoria</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>Medidores</t>
+          <t>medidores</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>30770148</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>000089</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>ALFARO LUQUE, MARIA</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE PACHAYZA</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>AV. PACHAYZA 5</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>6579582</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>29302445</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>000055</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>ALFARO NAVINTA, ANIBAL</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO CENTRO</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>6587782</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>30769528</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>000498</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>ALFARO NEYRA DE CHUQUIYANQUI LUCIA POMPEYA</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE CHAUPI</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>AV. CENTENARIO 102</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>60062505</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>45209656</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>000308</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>ALFARO TORREZ, TATIANA PAOLA</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE CHAUPI</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>JR. LIMA 45</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>60062454,18052517</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>30769348</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>000274</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>ALVAREZ VERA LELIS SOLNA</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE CHAUPI</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>CALLE CHAUPI 12</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>009174</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>46981924</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>000746</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>ANGULO ESCOBAR, JEISVER ANTONIO</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE CHAUPI</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>AV. CIRCUNVALACION 88</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>23022187</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>SD-001</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>000092</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>ANTACHOQUE ANCO, YULY INES</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE PACHAYZA</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>AV. PACHAYZA 10</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>21003057</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>30771072</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>000002</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>ANTACHOQUE MOTA, JUANA HILDA</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE LUCMANI</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>SECTOR LUCMANI 14</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>6659764</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>30769540</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>000004</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>ANTACHOQUE VERA, JUAN JUSTO</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE LUCMANI</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>SECTOR LUCMANI 22</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>6585597</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>02434916</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>000095</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>APAZA QUISPE, JOSE</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE PACHAYZA</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>JR. GRAU 44</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>6659519</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>30770030</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>AYMARA HUAMANI, ALEJA</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE LUCMANI</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>SECTOR LUCMANI 30</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>6582810</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>30770213</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>000007</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>CABRERA CHAVEZ, ASISCLO</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE LUCMANI</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>SECTOR LUCMANI 45</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>23015480</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>02150722</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>000066</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>CALLA HUARSAYA, LUIS</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO ALTO</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>6659665</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>30769551-1</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>000098</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>CARPIO HUAMANI, JUAN VITALIANO</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE PACHAYZA</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>JR. BOLOGNESI 15</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>6587963</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>30769551-2</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>000099</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>CARPIO LAZARO, NANCY CELSA</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE PACHAYZA</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>JR. BOLOGNESI 17</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>6579722</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>80313677</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>000704</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>CASTRO USCAMAYTA ELIANA</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA S/N</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>220017513</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>30769698</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>000059</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>CHALCO CORIMANYA, BLANCA DELIA</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO S/N</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>6593586</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>30769343</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>000061</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>CHALCO HUAMANI, SAIDA</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>21003055</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>30771152</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>000527</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>CHAUCAYANQUI ALVAREZ, CARLOS ALEJO</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>2001887</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>30770229</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>000528</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CHAUCAYANQUI ALVAREZ, CLEMENTE</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>6593681</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>SD-026</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>000771</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>CONEXION SIN MEDIDOR 000771</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>BARRIO DE LUCMANI</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>LUCMANI S/N</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>SIN_MEDIDOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>000070</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>HUAMANI CASTRO, BERTHA</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>HUAQUILLO BAJO</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>6659861</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>30769321</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>000534</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>NEYRA DE USCAMAYTA, MANUELA ANA</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA S/N</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>6593461</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>30769931-1</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>000533</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>ROMERO CHAUCAYANQUI JUSTO MARCELO</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA S/N</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>6593433</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>30770890</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>000529</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>SURCO VILLENA, SUSY BETTY</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>220014925</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>30770036</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>000530</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>TORRES COA, CILA CAMILA</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>6563926</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>30778043</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>000531</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>TORRES HUAMANI, AMELIA BENITA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>AYACUCHO S/N</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>6563939</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>30769528</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>000498</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>ALFARO NEYRA DE CHUQUIYANQUI LUCIA POMPEYA</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE CHAUPI</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>AV. CENTENARIO 102</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>30769896</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>000536</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>USCAMAYTA NEYRA, DAVID JESUS</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>CHAUPICERCA S/N</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>60062505</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>45209656</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>000308</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>ALFARO TORREZ, TATIANA PAOLA</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE CHAUPI</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>JR. LIMA 45</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>60062454,18052517</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>30769348</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>000274</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>ALVAREZ VERA LELIS SOLNA</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE CHAUPI</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>CALLE CHAUPI 12</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>009174</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>46981924</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>000746</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>ANGULO ESCOBAR, JEISVER ANTONIO</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE CHAUPI</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>AV. CIRCUNVALACION 88</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>23022187</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>30771072</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>000002</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>ANTACHOQUE MOTA, JUANA HILDA</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE LUCMANI</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>SECTOR LUCMANI 14</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>6659764</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>30769540</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>000004</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ANTACHOQUE VERA, JUAN JUSTO</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE LUCMANI</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>SECTOR LUCMANI 22</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>6585597</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>30770030</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>000006</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>AYMARA HUAMANI, ALEJA</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE LUCMANI</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>SECTOR LUCMANI 30</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>6582810</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>30770213</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>000007</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>CABRERA CHAVEZ, ASISCLO</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE LUCMANI</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SECTOR LUCMANI 45</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>23015480</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>SD-026</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>000771</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>CONEXION SIN MEDIDOR 000771</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE LUCMANI</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>LUCMANI S/N</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>SIN_MEDIDOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>30770148</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>000089</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>ALFARO LUQUE, MARIA</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE PACHAYZA</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>AV. PACHAYZA 5</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>6579582</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>SD-001</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>000092</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>ANTACHOQUE ANCO, YULY INES</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE PACHAYZA</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>AV. PACHAYZA 10</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>21003057</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>02434916</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>000095</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>APAZA QUISPE, JOSE</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE PACHAYZA</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>JR. GRAU 44</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>6659519</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>30769551-1</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>000098</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>CARPIO HUAMANI, JUAN VITALIANO</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE PACHAYZA</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>JR. BOLOGNESI 15</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>6587963</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>30769551-2</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>000099</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>CARPIO LAZARO, NANCY CELSA</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>BARRIO DE PACHAYZA</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>JR. BOLOGNESI 17</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>6579722</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>80313677</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>000704</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>CASTRO USCAMAYTA ELIANA</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA S/N</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>220017513</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>30769321</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>000534</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>NEYRA DE USCAMAYTA, MANUELA ANA</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA S/N</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>6593461</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>30769931-1</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>000533</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>ROMERO CHAUCAYANQUI JUSTO MARCELO</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA S/N</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>6593433</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>30769896</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>000536</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>USCAMAYTA NEYRA, DAVID JESUS</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>CHAUPICERCA S/N</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>6593726</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>29302445</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>000055</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>ALFARO NAVINTA, ANIBAL</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO CENTRO</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>6587782</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>02150722</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>000066</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>CALLA HUARSAYA, LUIS</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO ALTO</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>6659665</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>30769698</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>000059</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>CHALCO CORIMANYA, BLANCA DELIA</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO S/N</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>6593586</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>30769343</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>000061</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>CHALCO HUAMANI, SAIDA</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>21003055</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>000070</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>HUAMANI CASTRO, BERTHA</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>HUAQUILLO BAJO</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>6659861</t>
         </is>
       </c>
     </row>
@@ -6460,42 +6506,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CONFIGURACIÓN GENERAL DEL SISTEMA (JSON COMPLETO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Esta celda (A4) contiene el JSON íntegro para restaurar parámetros, tarifas y sectores.</t>
-        </is>
-      </c>
-    </row>
+          <t>CAAPD ISPACAS — CONFIGURACIÓN DEL SISTEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>PARÁMETRO CLAVE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>JSON_CONFIG_COMPLETO</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>PARAMETRO</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>{
   "empresa": {
@@ -6551,6 +6597,50 @@
           "precio_m3": 4.0
         }
       ]
+    },
+    "B": {
+      "nombre": "Comercial",
+      "cargo_fijo": 2.5,
+      "tarifa_desague": 0.0,
+      "rangos": [
+        {
+          "m3_desde": 0,
+          "m3_hasta": 10,
+          "precio_m3": 1.5
+        },
+        {
+          "m3_desde": 10,
+          "m3_hasta": 20,
+          "precio_m3": 2.0
+        },
+        {
+          "m3_desde": 20,
+          "m3_hasta": null,
+          "precio_m3": 3.0
+        }
+      ]
+    },
+    "C": {
+      "nombre": "Estatal / Social",
+      "cargo_fijo": 1.5,
+      "tarifa_desague": 0.0,
+      "rangos": [
+        {
+          "m3_desde": 0,
+          "m3_hasta": 10,
+          "precio_m3": 1.0
+        },
+        {
+          "m3_desde": 10,
+          "m3_hasta": 20,
+          "precio_m3": 1.5
+        },
+        {
+          "m3_desde": 20,
+          "m3_hasta": null,
+          "precio_m3": 2.5
+        }
+      ]
     }
   },
   "lectores": {
@@ -6567,64 +6657,77 @@
     "estado": "CERRADO",
     "fecha_emision": "2026-08-26",
     "fecha_vencimiento": "2026-09-10"
-  }
+  },
+  "ultimo_envio_lectores": "2026-10-15 06:26:16"
 }</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ultimo_recibo</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Último Recibo</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>periodo_activo</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Periodo Actual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>estado_mes</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Estado Mes Actual</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>CERRADO</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>fecha_emision</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fecha Emisión</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>fecha_vencimiento</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fecha Vencimiento</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sectores</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AYACUCHO, CHAUPICERCA, BARRIO DE CHAUPI, BARRIO DE LUCMANI, BARRIO DE PACHAYZA, HUAQUILLO</t>
         </is>
       </c>
     </row>

--- a/Documents/caapd-facturacion/escritorio/Base de datos/PADRON_MES_2026-08.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos/PADRON_MES_2026-08.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15 06:26:17</t>
+          <t>2026-10-15 07:07:03</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
     "fecha_emision": "2026-08-26",
     "fecha_vencimiento": "2026-09-10"
   },
-  "ultimo_envio_lectores": "2026-10-15 06:26:16"
+  "ultimo_envio_lectores": "2026-10-15 07:07:03"
 }</t>
         </is>
       </c>
